--- a/data/trans_orig/IP07KS_C07_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP07KS_C07_2023-Estudios-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de trato justo por parte de sus padres en 2023 (tasa de respuesta: 99,83%)</t>
+          <t>Menores según la frecuencia de trato justo por parte de sus padres, percibida por el/la menor en 2023 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4326</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1725</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8405</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>26,75%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>10,67%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>51,98%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>6021</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2980</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>8902</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>48,53%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>24,02%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>71,75%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4319</t>
+          <t>6391</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1853</t>
+          <t>2596</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7906</t>
+          <t>9860</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>45,81%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,93%</t>
+          <t>70,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>10340</t>
+          <t>10717</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6158</t>
+          <t>6020</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15399</t>
+          <t>15975</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>53,91%</t>
+          <t>53,04%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>8933</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4869</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>12511</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>55,25%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>30,11%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>77,38%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>5834</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>3014</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>9070</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>47,03%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>24,3%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>73,11%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8972</t>
+          <t>6694</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5385</t>
+          <t>3233</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12329</t>
+          <t>10608</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>55,53%</t>
+          <t>47,99%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>76,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>14807</t>
+          <t>15628</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10171</t>
+          <t>10455</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19409</t>
+          <t>21292</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>51,84%</t>
+          <t>51,89%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>70,69%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2909</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>769</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>6979</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>17,99%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>4,76%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>43,17%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>551</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>865</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>4,45%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>3059</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>6,2%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>16,34%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>2866</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>859</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>6496</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>17,74%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>5,32%</t>
-        </is>
-      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>3418</t>
+          <t>3774</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1235</t>
+          <t>1504</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7054</t>
+          <t>7509</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,93%</t>
         </is>
       </c>
     </row>
@@ -1285,57 +1285,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>16168</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>16168</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>16168</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>12407</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>12407</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>12407</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16158</t>
+          <t>13950</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16158</t>
+          <t>13950</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16158</t>
+          <t>13950</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>28565</t>
+          <t>30119</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>28565</t>
+          <t>30119</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>28565</t>
+          <t>30119</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>126952</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>112107</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>143180</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>63,37%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>55,96%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>71,47%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>84671</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>47593</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>105301</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>53,15%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>29,87%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>66,1%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>130853</t>
+          <t>88283</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>113890</t>
+          <t>76755</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>147672</t>
+          <t>98102</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>64,56%</t>
+          <t>61,88%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>56,19%</t>
+          <t>53,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>72,85%</t>
+          <t>68,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>215524</t>
+          <t>215235</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>167870</t>
+          <t>197070</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>242983</t>
+          <t>235929</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>59,53%</t>
+          <t>62,75%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>46,37%</t>
+          <t>57,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>67,12%</t>
+          <t>68,78%</t>
         </is>
       </c>
     </row>
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>60193</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>45623</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>74697</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>30,05%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>22,77%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>37,29%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>68808</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>47100</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>108469</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>43,19%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>29,56%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>68,09%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>58745</t>
+          <t>48181</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>44046</t>
+          <t>38089</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>76245</t>
+          <t>59456</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>33,77%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>41,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>127553</t>
+          <t>108374</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>100671</t>
+          <t>89166</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>184190</t>
+          <t>125153</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>50,88%</t>
+          <t>36,49%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>8338</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>3766</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>16545</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>4,16%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1,88%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>8,26%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>5391</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>2088</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>11084</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>3,38%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>6,96%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>8301</t>
+          <t>5820</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3626</t>
+          <t>2483</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16199</t>
+          <t>11286</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>13692</t>
+          <t>14158</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>8173</t>
+          <t>8144</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>23056</t>
+          <t>23508</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,85%</t>
         </is>
       </c>
     </row>
@@ -1741,107 +1741,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1187</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4083</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,04%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1158</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1187</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3834</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>3680</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1,89%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1158</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>4069</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -1854,107 +1854,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3664</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>953</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>9147</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1,83%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>4,57%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>444</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>385</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2223</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>1955</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>4049</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>973</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>8956</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>1,18%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,28%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>3643</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>961</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>8805</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>1,8%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>4,34%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>4086</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>1581</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>9937</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>1,13%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -1967,57 +1967,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>200333</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>200333</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>200333</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>195</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>159313</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>159313</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>159313</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>217</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>202700</t>
+          <t>142669</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>202700</t>
+          <t>142669</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>202700</t>
+          <t>142669</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>362013</t>
+          <t>343002</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>362013</t>
+          <t>343002</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>362013</t>
+          <t>343002</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2084,72 +2084,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>42440</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>36368</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>47228</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>80,07%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>68,61%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>89,1%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>29279</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>24683</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>33326</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>75,56%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>63,69%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>86,0%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>42796</t>
+          <t>30937</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>36637</t>
+          <t>25662</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>46602</t>
+          <t>35085</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>75,51%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>69,53%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>85,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>72075</t>
+          <t>73377</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>64338</t>
+          <t>65736</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>77849</t>
+          <t>80187</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>78,82%</t>
+          <t>78,08%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>70,36%</t>
+          <t>69,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>85,33%</t>
         </is>
       </c>
     </row>
@@ -2197,72 +2197,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>9648</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>5105</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>15280</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>18,2%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>9,63%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>28,83%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>8299</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>4256</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>12795</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>21,42%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>10,98%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>33,02%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>8983</t>
+          <t>8892</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5130</t>
+          <t>4926</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14819</t>
+          <t>14089</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>17282</t>
+          <t>18540</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>11653</t>
+          <t>12119</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>25048</t>
+          <t>26145</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>27,82%</t>
         </is>
       </c>
     </row>
@@ -2310,107 +2310,107 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>736</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>777</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>4221</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>3966</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>1,9%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>10,89%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>9,68%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>777</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>3234</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>736</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>4899</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>438</t>
+          <t>917</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2551,12 +2551,12 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2519</t>
+          <t>5380</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>914</t>
+          <t>363</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2586,12 +2586,12 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>2732</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>1352</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>348</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,61%</t>
         </is>
       </c>
     </row>
@@ -2649,57 +2649,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>53004</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>53004</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>53004</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>38752</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>38752</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>38752</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>52693</t>
+          <t>40969</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>52693</t>
+          <t>40969</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>52693</t>
+          <t>40969</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>91445</t>
+          <t>93974</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>91445</t>
+          <t>93974</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>91445</t>
+          <t>93974</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2766,72 +2766,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>173717</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>158483</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>190640</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>64,46%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>58,81%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>70,74%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>178</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>119971</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>77142</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>142857</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>57,0%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>36,65%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>67,87%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>177968</t>
+          <t>125611</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>160102</t>
+          <t>112461</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>196191</t>
+          <t>137135</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>65,54%</t>
+          <t>63,57%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>58,96%</t>
+          <t>56,92%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>72,25%</t>
+          <t>69,4%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>297939</t>
+          <t>299328</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>244150</t>
+          <t>278565</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>323177</t>
+          <t>319241</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>61,81%</t>
+          <t>64,08%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>50,65%</t>
+          <t>59,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>67,05%</t>
+          <t>68,35%</t>
         </is>
       </c>
     </row>
@@ -2879,72 +2879,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>78774</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>62124</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>94734</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>29,23%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>23,05%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>35,15%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>82942</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>59446</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>128532</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>39,41%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>28,24%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>61,07%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>76700</t>
+          <t>63767</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>60352</t>
+          <t>52548</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>92616</t>
+          <t>76563</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>38,75%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>159642</t>
+          <t>142542</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>131933</t>
+          <t>124656</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>215864</t>
+          <t>162755</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>34,84%</t>
         </is>
       </c>
     </row>
@@ -2992,72 +2992,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>11247</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>5942</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>19873</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>4,17%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>2,2%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>7,37%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>6678</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>3019</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>13389</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>3,17%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>6,36%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>11168</t>
+          <t>7462</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5707</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>19458</t>
+          <t>12751</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>17846</t>
+          <t>18709</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>11358</t>
+          <t>11895</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>27153</t>
+          <t>27953</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,98%</t>
         </is>
       </c>
     </row>
@@ -3105,107 +3105,107 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>1187</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>4234</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="M25" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="P25" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="Q25" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>1158</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>1187</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>3660</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>4252</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>0,25%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>1158</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>3755</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -3218,72 +3218,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>4580</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>1714</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>9660</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>1,7%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>3,58%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>881</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>748</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>2735</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>2712</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>4557</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>10860</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>1,68%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>5438</t>
+          <t>5328</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>2235</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>11144</t>
+          <t>11142</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -3331,57 +3331,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>269506</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>269506</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>269506</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>270</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>271551</t>
+          <t>197588</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>271551</t>
+          <t>197588</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>271551</t>
+          <t>197588</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>482023</t>
+          <t>467094</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>482023</t>
+          <t>467094</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>482023</t>
+          <t>467094</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
